--- a/314e-ig/output/StructureDefinition-visionprescription-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-visionprescription-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-visionprescription-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-visionprescription-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-visionprescription-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-visionprescription-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-visionprescription-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-visionprescription-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -570,7 +570,7 @@
     <t>VisionPrescription.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -598,7 +598,7 @@
     <t>VisionPrescription.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -654,7 +654,7 @@
     <t>VisionPrescription.prescriber</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1277,7 +1277,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="81.578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="158.1328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/314e-ig/output/StructureDefinition-visionprescription-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-visionprescription-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-visionprescription-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-visionprescription-314e.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="309">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -445,6 +445,27 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
+    <t>VisionPrescription.extension:cosigner</t>
+  </si>
+  <si>
+    <t>cosigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/resource-cosigner}
+</t>
+  </si>
+  <si>
+    <t>Individual who co-signed or verified this vision prescription</t>
+  </si>
+  <si>
+    <t>Identifies an individual who reviewed, verified, or co-signed the associated
+clinical document, note, order, or healthcare record, alongside the primary author or requester.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>VisionPrescription.extension:additionalInfo</t>
   </si>
   <si>
@@ -461,10 +482,6 @@
     <t>Applied at the root level of any resource. Used to capture supplementary
 or non-standard information related to a FHIR resource that is not
 represented by the core FHIR elements or existing profiles.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
   </si>
   <si>
     <t>VisionPrescription.modifierExtension</t>
@@ -1264,7 +1281,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN41"/>
+  <dimension ref="A1:AN42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.59375" customWidth="true" bestFit="true"/>
@@ -2352,7 +2369,7 @@
         <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
@@ -2453,11 +2470,13 @@
         <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="D11" t="s" s="2">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2470,26 +2489,22 @@
         <v>20</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="O11" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>20</v>
       </c>
@@ -2537,7 +2552,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2546,7 +2561,7 @@
         <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>20</v>
+        <v>143</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>137</v>
@@ -2555,7 +2570,7 @@
         <v>20</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>20</v>
@@ -2566,14 +2581,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2586,23 +2601,25 @@
         <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -2651,7 +2668,7 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2663,27 +2680,27 @@
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>156</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>158</v>
+        <v>20</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>159</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2691,34 +2708,32 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>106</v>
+        <v>157</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -2743,13 +2758,13 @@
         <v>20</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>20</v>
@@ -2767,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
@@ -2782,24 +2797,24 @@
         <v>98</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>20</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2816,23 +2831,25 @@
         <v>20</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>172</v>
+        <v>106</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="O14" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -2857,13 +2874,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -2881,7 +2898,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>86</v>
@@ -2896,13 +2913,13 @@
         <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>20</v>
+        <v>175</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>20</v>
@@ -3010,24 +3027,24 @@
         <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>181</v>
+        <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>182</v>
+        <v>20</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>183</v>
+        <v>20</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>184</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3035,7 +3052,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>86</v>
@@ -3047,20 +3064,20 @@
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3109,10 +3126,10 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>86</v>
@@ -3124,24 +3141,24 @@
         <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3149,7 +3166,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>86</v>
@@ -3161,22 +3178,20 @@
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>198</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -3225,10 +3240,10 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>86</v>
@@ -3240,24 +3255,24 @@
         <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3280,17 +3295,19 @@
         <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="O18" t="s" s="2">
-        <v>207</v>
+        <v>180</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3339,7 +3356,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>86</v>
@@ -3354,24 +3371,24 @@
         <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3382,7 +3399,7 @@
         <v>86</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3394,16 +3411,18 @@
         <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+      <c r="O19" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
       </c>
@@ -3451,13 +3470,13 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>86</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
@@ -3466,16 +3485,16 @@
         <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>20</v>
+        <v>213</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -3491,10 +3510,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -3503,7 +3522,7 @@
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>218</v>
@@ -3563,25 +3582,25 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>20</v>
@@ -3592,21 +3611,21 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -3618,7 +3637,7 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>131</v>
+        <v>223</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>224</v>
@@ -3626,9 +3645,7 @@
       <c r="M21" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="N21" t="s" s="2">
-        <v>148</v>
-      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -3683,19 +3700,19 @@
         <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>20</v>
@@ -3706,14 +3723,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>228</v>
+        <v>150</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3726,10 +3743,10 @@
         <v>20</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
         <v>131</v>
@@ -3741,11 +3758,9 @@
         <v>230</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>20</v>
       </c>
@@ -3811,7 +3826,7 @@
         <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>129</v>
+        <v>227</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>20</v>
@@ -3829,26 +3844,26 @@
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>20</v>
+        <v>233</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>233</v>
+        <v>131</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>234</v>
@@ -3856,9 +3871,11 @@
       <c r="M23" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="N23" s="2"/>
+      <c r="N23" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O23" t="s" s="2">
-        <v>236</v>
+        <v>154</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -3883,13 +3900,13 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>238</v>
+        <v>20</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>239</v>
+        <v>20</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
@@ -3907,39 +3924,39 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>240</v>
+        <v>129</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3962,19 +3979,17 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -3999,13 +4014,13 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>165</v>
+        <v>242</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -4023,7 +4038,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>86</v>
@@ -4041,21 +4056,21 @@
         <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>20</v>
+        <v>246</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4063,7 +4078,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>86</v>
@@ -4075,22 +4090,22 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4115,13 +4130,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>20</v>
+        <v>252</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>20</v>
+        <v>253</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4139,10 +4154,10 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>86</v>
@@ -4157,7 +4172,7 @@
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>20</v>
@@ -4168,10 +4183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4194,7 +4209,7 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>256</v>
@@ -4202,9 +4217,11 @@
       <c r="M26" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="N26" s="2"/>
+      <c r="N26" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O26" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4253,7 +4270,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4271,7 +4288,7 @@
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>20</v>
@@ -4282,10 +4299,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4308,19 +4325,17 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4369,7 +4384,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4387,7 +4402,7 @@
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>20</v>
@@ -4412,7 +4427,7 @@
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -4424,17 +4439,19 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>213</v>
+        <v>264</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O28" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -4489,7 +4506,7 @@
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
@@ -4501,7 +4518,7 @@
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>20</v>
+        <v>227</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>20</v>
@@ -4512,10 +4529,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4526,7 +4543,7 @@
         <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -4541,13 +4558,15 @@
         <v>218</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>219</v>
+        <v>269</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+      <c r="O29" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
       </c>
@@ -4595,25 +4614,25 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>221</v>
+        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>20</v>
@@ -4624,21 +4643,21 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -4650,7 +4669,7 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>131</v>
+        <v>223</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>224</v>
@@ -4658,9 +4677,7 @@
       <c r="M30" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="N30" t="s" s="2">
-        <v>148</v>
-      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -4715,19 +4732,19 @@
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>20</v>
@@ -4738,14 +4755,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>228</v>
+        <v>150</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4758,10 +4775,10 @@
         <v>20</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>131</v>
@@ -4773,11 +4790,9 @@
         <v>230</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
@@ -4843,7 +4858,7 @@
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>129</v>
+        <v>227</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>20</v>
@@ -4854,43 +4869,45 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>20</v>
+        <v>233</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>250</v>
+        <v>131</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O32" t="s" s="2">
-        <v>254</v>
+        <v>154</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -4939,25 +4956,25 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>222</v>
+        <v>129</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>20</v>
@@ -4968,10 +4985,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4994,17 +5011,17 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>106</v>
+        <v>255</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5029,13 +5046,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>275</v>
+        <v>20</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>276</v>
+        <v>20</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5053,7 +5070,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>86</v>
@@ -5071,7 +5088,7 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
@@ -5093,7 +5110,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>86</v>
@@ -5108,7 +5125,7 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>250</v>
+        <v>106</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>278</v>
@@ -5118,7 +5135,7 @@
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5143,13 +5160,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>20</v>
+        <v>281</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5170,7 +5187,7 @@
         <v>277</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>86</v>
@@ -5185,7 +5202,7 @@
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>20</v>
@@ -5196,10 +5213,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5222,17 +5239,17 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5281,7 +5298,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5299,7 +5316,7 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>20</v>
@@ -5310,10 +5327,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5336,17 +5353,17 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5395,7 +5412,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5413,7 +5430,7 @@
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>20</v>
@@ -5424,10 +5441,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5450,17 +5467,17 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -5509,7 +5526,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5527,7 +5544,7 @@
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>20</v>
@@ -5538,10 +5555,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5564,17 +5581,17 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -5623,7 +5640,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5641,7 +5658,7 @@
         <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>20</v>
@@ -5652,10 +5669,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5678,17 +5695,17 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>218</v>
+        <v>296</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -5737,7 +5754,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5755,7 +5772,7 @@
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>20</v>
@@ -5766,10 +5783,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5792,17 +5809,17 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>254</v>
+        <v>288</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -5851,7 +5868,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5869,7 +5886,7 @@
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>20</v>
@@ -5880,10 +5897,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5894,7 +5911,7 @@
         <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -5906,17 +5923,17 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>301</v>
+        <v>223</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -5965,13 +5982,13 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
@@ -5983,12 +6000,126 @@
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN41" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="P42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>20</v>
       </c>
     </row>
